--- a/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2748400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2566100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2329100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1725600</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>818400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>603700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>441200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>365000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>273500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>195600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>125000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>74600</v>
       </c>
-      <c r="O8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>823000</v>
+      </c>
+      <c r="E9" s="3">
         <v>744600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>654500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>464700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>271000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>190800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>150200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>123300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>97000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>73600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>47800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>24500</v>
       </c>
-      <c r="O9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>1925400</v>
+      </c>
+      <c r="E10" s="3">
         <v>1821500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1674600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1260900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>547300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>412900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>291000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>241600</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>176500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>122000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>77200</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>50100</v>
       </c>
-      <c r="O10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -862,50 +874,54 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>455800</v>
+      </c>
+      <c r="E12" s="3">
         <v>412400</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>271500</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>180100</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>121900</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>97400</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>71400</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>55100</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>42700</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>36600</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>27500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>18700</v>
       </c>
-      <c r="O12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,33 +961,36 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>97300</v>
+      </c>
+      <c r="E14" s="3">
         <v>1045000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>16900</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>-200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>17100</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K14" s="3" t="s">
         <v>3</v>
       </c>
@@ -987,9 +1006,12 @@
       <c r="O14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1029,9 +1051,12 @@
       <c r="O15" s="3">
         <v>0</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P15" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2471200</v>
+      </c>
+      <c r="E17" s="3">
         <v>3224700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1863400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1318500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>729600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>528900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>429300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>347400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>275400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>201800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>124300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>76000</v>
       </c>
-      <c r="O17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>277200</v>
+      </c>
+      <c r="E18" s="3">
         <v>-658600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>465700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>407200</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>88800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>74800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>11900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>17600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-1900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-6300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-1400</v>
       </c>
-      <c r="O18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>29700</v>
+      </c>
+      <c r="E20" s="3">
         <v>10800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>15800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>16200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>31500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-13200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-24600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>398200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-551100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>555800</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>465900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>153000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>104000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>70600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-7900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>7600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>12700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>5900</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14000</v>
+      </c>
+      <c r="E22" s="3">
         <v>14200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>42000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>24300</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>7200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>500</v>
       </c>
-      <c r="O22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>292800</v>
+      </c>
+      <c r="E23" s="3">
         <v>-662000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>471700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>365700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>80600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>55100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-2900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-28000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-2500</v>
       </c>
-      <c r="O23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-17800</v>
+      </c>
+      <c r="E24" s="3">
         <v>28700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-16700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>12500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-11100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-26300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-18400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26100</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-100</v>
       </c>
-      <c r="O24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>310600</v>
+      </c>
+      <c r="E26" s="3">
         <v>-690700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>488400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>353200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>91700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>81400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>50700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-29900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-54100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-15200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-2400</v>
       </c>
-      <c r="O26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>310600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-690700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>488400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>353200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>91700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>81400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>50600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-29900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-54100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-15200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-2600</v>
       </c>
-      <c r="O27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,33 +1581,36 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="E29" s="3">
         <v>-3600</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>5200</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-3900</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>4200</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-3900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>31100</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
       </c>
@@ -1566,9 +1626,12 @@
       <c r="O29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-29700</v>
+      </c>
+      <c r="E32" s="3">
         <v>-10800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-15800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-16200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-31500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>13200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>24600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>307600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-694300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>493500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>349200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>95900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>77500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>81700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-29900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-54100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-15200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-800</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-2600</v>
       </c>
-      <c r="O33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>307600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-694300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>493500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>349200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>95900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>77500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>81700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-29900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-54100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-15200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-800</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-2600</v>
       </c>
-      <c r="O35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,134 +1987,144 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>914300</v>
+      </c>
+      <c r="E41" s="3">
         <v>921300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>780200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>1244100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>443300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>367000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>315400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>181600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>271200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>69700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>36800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>34900</v>
       </c>
-      <c r="O41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>236100</v>
+      </c>
+      <c r="E42" s="3">
         <v>250400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>204400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>425100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>374000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>257300</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>25100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>100500</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>21600</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>19200</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18100</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>20800</v>
       </c>
-      <c r="O42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>290100</v>
+      </c>
+      <c r="E43" s="3">
         <v>261800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>247500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>169400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>65200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>33300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>78300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>56200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>39500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>26000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>16400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9500</v>
       </c>
-      <c r="O43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2069,111 +2164,120 @@
       <c r="O44" s="3">
         <v>0</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>129900</v>
+      </c>
+      <c r="E45" s="3">
         <v>80200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>109400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>56200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>38600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22700</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>32700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>26700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>15200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>5500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3500</v>
       </c>
-      <c r="O45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1570400</v>
+      </c>
+      <c r="E46" s="3">
         <v>1513700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1341500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1894800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>921000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>680300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>439300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>371000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>359100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>127100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>76800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>68800</v>
       </c>
-      <c r="O46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>86700</v>
+      </c>
+      <c r="E47" s="3">
         <v>29100</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>85000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>39100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>89300</v>
       </c>
-      <c r="H47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="I47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2189,99 +2293,108 @@
       <c r="M47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="N47" s="3">
-        <v>0</v>
+      <c r="N47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="O47" s="3">
         <v>0</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P47" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>291900</v>
+      </c>
+      <c r="E48" s="3">
         <v>288500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>321000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>132100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>169200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>120200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>117600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>126400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>105000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>151100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>23100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18200</v>
       </c>
-      <c r="O48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>595500</v>
+      </c>
+      <c r="E49" s="3">
         <v>673100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1978200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>328300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>338000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>72100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>42600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>43200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>30600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>41700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>5800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5300</v>
       </c>
-      <c r="O49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>140800</v>
+      </c>
+      <c r="E52" s="3">
         <v>130400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>106000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>10300</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>29300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>6100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>40600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7400</v>
-      </c>
-      <c r="M52" s="3">
-        <v>400</v>
       </c>
       <c r="N52" s="3">
         <v>400</v>
       </c>
-      <c r="O52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O52" s="3">
+        <v>400</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2685400</v>
+      </c>
+      <c r="E54" s="3">
         <v>2635000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3831800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2404500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>1542400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>901900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>605600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>581200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>553100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>246200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>106200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>92600</v>
       </c>
-      <c r="O54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>29900</v>
+      </c>
+      <c r="E57" s="3">
         <v>28800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>40900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>26300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>13600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>11000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>14400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>8200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5300</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>3500</v>
       </c>
-      <c r="O57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E58" s="3">
         <v>4700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>2400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>8300</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>3900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1300</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>674800</v>
+      </c>
+      <c r="E59" s="3">
         <v>598300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>585200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>405200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>153900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>81600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>83100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>66200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>60100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>31500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>13100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6200</v>
       </c>
-      <c r="O59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>710800</v>
+      </c>
+      <c r="E60" s="3">
         <v>631800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>615600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>454700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>188500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>112100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>102500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>80100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>41500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>19200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10900</v>
       </c>
-      <c r="O60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2383400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2385300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2385700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1107300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>838700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>278600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>4100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>3100</v>
       </c>
-      <c r="M61" s="3">
-        <v>0</v>
-      </c>
       <c r="N61" s="3">
+        <v>0</v>
+      </c>
+      <c r="O61" s="3">
         <v>800</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>134900</v>
+      </c>
+      <c r="E62" s="3">
         <v>165100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>201900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>100100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>108500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>110300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>102100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>147100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>134900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>54300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>2700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1000</v>
       </c>
-      <c r="O62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3229100</v>
+      </c>
+      <c r="E66" s="3">
         <v>3182200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3203200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>1662100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1135700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>501000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>208700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>236400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>222600</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>98900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>21900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>12700</v>
       </c>
-      <c r="O66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3078,7 +3245,7 @@
         <v>0</v>
       </c>
       <c r="L70" s="3">
-        <v>80200</v>
+        <v>0</v>
       </c>
       <c r="M70" s="3">
         <v>80200</v>
@@ -3087,11 +3254,14 @@
         <v>80200</v>
       </c>
       <c r="O70" s="3">
-        <v>0</v>
-      </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+        <v>80200</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1357400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1048300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>71700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-146800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-227400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-153400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-96300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-116300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-86400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-32400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-17100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-16000</v>
       </c>
-      <c r="O72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-543700</v>
+      </c>
+      <c r="E76" s="3">
         <v>-547300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>628600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>742400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>406600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>400900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>396900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>344800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>330500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>67100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>4000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-300</v>
       </c>
-      <c r="O76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>307600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-694300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>493500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>349200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>95900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>77500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>81700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-29900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-54100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-15200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-800</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-2600</v>
       </c>
-      <c r="O81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>91300</v>
+      </c>
+      <c r="E83" s="3">
         <v>96700</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>74300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>58200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>48000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>26700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>27200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>22500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>18600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>17200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>12400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>7900</v>
       </c>
-      <c r="O83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>705500</v>
+      </c>
+      <c r="E89" s="3">
         <v>683600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>651600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>679000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>206900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>198900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>69100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>48000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>33200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>12100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>16500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>9700</v>
       </c>
-      <c r="O89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-16700</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-36500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11100</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-6500</v>
       </c>
-      <c r="O91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-73300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-30000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-1558000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-488400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-285400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>61800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-135400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-23300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-20700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-15000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-28900</v>
       </c>
-      <c r="O94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,8 +4221,9 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4030,9 +4263,12 @@
       <c r="O96" s="3">
         <v>0</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,133 +4398,145 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-656500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-506500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>452700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>119300</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>359600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>144000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>6600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>195700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>45200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>43000</v>
       </c>
-      <c r="O100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-10200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>13900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-3600</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-1700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-4000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>400</v>
       </c>
-      <c r="N101" s="3">
-        <v>0</v>
-      </c>
-      <c r="O101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="O101" s="3">
+        <v>0</v>
+      </c>
+      <c r="P101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-12300</v>
+      </c>
+      <c r="E102" s="3">
         <v>141100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-463900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>800800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>76300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>51500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>133900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-89700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>201600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>32900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>23800</v>
       </c>
-      <c r="O102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="P102" s="3"/>
+      <c r="P102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
   <si>
     <t>ETSY</t>
   </si>
@@ -896,7 +896,7 @@
         <v>121900</v>
       </c>
       <c r="I12" s="3">
-        <v>97400</v>
+        <v>97200</v>
       </c>
       <c r="J12" s="3">
         <v>71400</v>
@@ -971,22 +971,22 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>97300</v>
+        <v>98500</v>
       </c>
       <c r="E14" s="3">
-        <v>1045000</v>
+        <v>1047900</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>36700</v>
       </c>
       <c r="G14" s="3">
-        <v>16900</v>
+        <v>18700</v>
       </c>
       <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-200</v>
+        <v>3900</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="J14" s="3">
         <v>17100</v>
@@ -1016,25 +1016,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>57000</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>59400</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>44300</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>35600</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>17200</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>19000</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2471200</v>
+        <v>2372700</v>
       </c>
       <c r="E17" s="3">
-        <v>3224700</v>
+        <v>2176800</v>
       </c>
       <c r="F17" s="3">
-        <v>1863400</v>
+        <v>1826700</v>
       </c>
       <c r="G17" s="3">
-        <v>1318500</v>
+        <v>1299800</v>
       </c>
       <c r="H17" s="3">
-        <v>729600</v>
+        <v>725700</v>
       </c>
       <c r="I17" s="3">
         <v>528900</v>
       </c>
       <c r="J17" s="3">
-        <v>429300</v>
+        <v>412300</v>
       </c>
       <c r="K17" s="3">
         <v>347400</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>277200</v>
+        <v>375700</v>
       </c>
       <c r="E18" s="3">
-        <v>-658600</v>
+        <v>389300</v>
       </c>
       <c r="F18" s="3">
-        <v>465700</v>
+        <v>502400</v>
       </c>
       <c r="G18" s="3">
-        <v>407200</v>
+        <v>425800</v>
       </c>
       <c r="H18" s="3">
-        <v>88800</v>
+        <v>92700</v>
       </c>
       <c r="I18" s="3">
         <v>74800</v>
       </c>
       <c r="J18" s="3">
-        <v>11900</v>
+        <v>29000</v>
       </c>
       <c r="K18" s="3">
         <v>17600</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>29700</v>
+        <v>6300</v>
       </c>
       <c r="E20" s="3">
-        <v>10800</v>
+        <v>200</v>
       </c>
       <c r="F20" s="3">
-        <v>15800</v>
+        <v>-13700</v>
       </c>
       <c r="G20" s="3">
-        <v>600</v>
+        <v>6500</v>
       </c>
       <c r="H20" s="3">
-        <v>16200</v>
+        <v>-3000</v>
       </c>
       <c r="I20" s="3">
-        <v>2500</v>
+        <v>6500</v>
       </c>
       <c r="J20" s="3">
-        <v>31500</v>
+        <v>-29100</v>
       </c>
       <c r="K20" s="3">
         <v>-13200</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>398200</v>
+        <v>426400</v>
       </c>
       <c r="E21" s="3">
-        <v>-551100</v>
+        <v>448500</v>
       </c>
       <c r="F21" s="3">
-        <v>555800</v>
+        <v>560400</v>
       </c>
       <c r="G21" s="3">
-        <v>465900</v>
+        <v>454900</v>
       </c>
       <c r="H21" s="3">
-        <v>153000</v>
+        <v>125000</v>
       </c>
       <c r="I21" s="3">
-        <v>104000</v>
+        <v>85500</v>
       </c>
       <c r="J21" s="3">
-        <v>70600</v>
+        <v>77100</v>
       </c>
       <c r="K21" s="3">
         <v>26900</v>
@@ -1366,25 +1366,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>-17800</v>
+        <v>-14700</v>
       </c>
       <c r="E24" s="3">
-        <v>28700</v>
+        <v>32300</v>
       </c>
       <c r="F24" s="3">
-        <v>-16700</v>
+        <v>-21900</v>
       </c>
       <c r="G24" s="3">
-        <v>12500</v>
+        <v>16500</v>
       </c>
       <c r="H24" s="3">
-        <v>-11100</v>
+        <v>-15200</v>
       </c>
       <c r="I24" s="3">
-        <v>-26300</v>
+        <v>-22400</v>
       </c>
       <c r="J24" s="3">
-        <v>-18400</v>
+        <v>-49500</v>
       </c>
       <c r="K24" s="3">
         <v>27000</v>
@@ -1456,25 +1456,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>310600</v>
+        <v>307600</v>
       </c>
       <c r="E26" s="3">
-        <v>-690700</v>
+        <v>-694300</v>
       </c>
       <c r="F26" s="3">
-        <v>488400</v>
+        <v>493500</v>
       </c>
       <c r="G26" s="3">
-        <v>353200</v>
+        <v>349200</v>
       </c>
       <c r="H26" s="3">
-        <v>91700</v>
+        <v>95900</v>
       </c>
       <c r="I26" s="3">
-        <v>81400</v>
+        <v>77500</v>
       </c>
       <c r="J26" s="3">
-        <v>50700</v>
+        <v>81800</v>
       </c>
       <c r="K26" s="3">
         <v>-29900</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>310600</v>
+        <v>307600</v>
       </c>
       <c r="E27" s="3">
-        <v>-690700</v>
+        <v>-694300</v>
       </c>
       <c r="F27" s="3">
-        <v>488400</v>
+        <v>493500</v>
       </c>
       <c r="G27" s="3">
-        <v>353200</v>
+        <v>349300</v>
       </c>
       <c r="H27" s="3">
-        <v>91700</v>
+        <v>95900</v>
       </c>
       <c r="I27" s="3">
-        <v>81400</v>
+        <v>77500</v>
       </c>
       <c r="J27" s="3">
-        <v>50600</v>
+        <v>81700</v>
       </c>
       <c r="K27" s="3">
         <v>-29900</v>
@@ -1591,25 +1591,25 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>-3100</v>
+        <v>0</v>
       </c>
       <c r="E29" s="3">
-        <v>-3600</v>
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>5200</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-3900</v>
+        <v>0</v>
       </c>
       <c r="H29" s="3">
-        <v>4200</v>
+        <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>-3900</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>31100</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>3</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-29700</v>
+        <v>-6300</v>
       </c>
       <c r="E32" s="3">
-        <v>-10800</v>
+        <v>-200</v>
       </c>
       <c r="F32" s="3">
-        <v>-15800</v>
+        <v>13700</v>
       </c>
       <c r="G32" s="3">
-        <v>-600</v>
+        <v>-6500</v>
       </c>
       <c r="H32" s="3">
-        <v>-16200</v>
+        <v>3000</v>
       </c>
       <c r="I32" s="3">
-        <v>-2500</v>
+        <v>-6500</v>
       </c>
       <c r="J32" s="3">
-        <v>-31500</v>
+        <v>29100</v>
       </c>
       <c r="K32" s="3">
         <v>13200</v>
@@ -1789,7 +1789,7 @@
         <v>77500</v>
       </c>
       <c r="J33" s="3">
-        <v>81700</v>
+        <v>81800</v>
       </c>
       <c r="K33" s="3">
         <v>-29900</v>
@@ -1879,7 +1879,7 @@
         <v>77500</v>
       </c>
       <c r="J35" s="3">
-        <v>81700</v>
+        <v>81800</v>
       </c>
       <c r="K35" s="3">
         <v>-29900</v>
@@ -2084,25 +2084,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>290100</v>
+        <v>24700</v>
       </c>
       <c r="E43" s="3">
-        <v>261800</v>
+        <v>27900</v>
       </c>
       <c r="F43" s="3">
-        <v>247500</v>
+        <v>27300</v>
       </c>
       <c r="G43" s="3">
-        <v>169400</v>
+        <v>22600</v>
       </c>
       <c r="H43" s="3">
-        <v>65200</v>
+        <v>15400</v>
       </c>
       <c r="I43" s="3">
-        <v>33300</v>
+        <v>12200</v>
       </c>
       <c r="J43" s="3">
-        <v>78300</v>
+        <v>33700</v>
       </c>
       <c r="K43" s="3">
         <v>56200</v>
@@ -2128,26 +2128,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>129900</v>
+        <v>265400</v>
       </c>
       <c r="E45" s="3">
-        <v>80200</v>
+        <v>234000</v>
       </c>
       <c r="F45" s="3">
-        <v>109400</v>
+        <v>220200</v>
       </c>
       <c r="G45" s="3">
-        <v>56200</v>
+        <v>146800</v>
       </c>
       <c r="H45" s="3">
-        <v>38600</v>
+        <v>49800</v>
       </c>
       <c r="I45" s="3">
-        <v>22700</v>
+        <v>21100</v>
       </c>
       <c r="J45" s="3">
-        <v>20400</v>
+        <v>44700</v>
       </c>
       <c r="K45" s="3">
         <v>32700</v>
@@ -2321,13 +2321,13 @@
         <v>132100</v>
       </c>
       <c r="H48" s="3">
-        <v>169200</v>
+        <v>66800</v>
       </c>
       <c r="I48" s="3">
-        <v>120200</v>
+        <v>89400</v>
       </c>
       <c r="J48" s="3">
-        <v>117600</v>
+        <v>99300</v>
       </c>
       <c r="K48" s="3">
         <v>126400</v>
@@ -2366,13 +2366,13 @@
         <v>328300</v>
       </c>
       <c r="H49" s="3">
-        <v>338000</v>
+        <v>440400</v>
       </c>
       <c r="I49" s="3">
-        <v>72100</v>
+        <v>102900</v>
       </c>
       <c r="J49" s="3">
-        <v>42600</v>
+        <v>61000</v>
       </c>
       <c r="K49" s="3">
         <v>43200</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>140800</v>
+        <v>3000</v>
       </c>
       <c r="E52" s="3">
-        <v>130400</v>
+        <v>8900</v>
       </c>
       <c r="F52" s="3">
-        <v>106000</v>
+        <v>10200</v>
       </c>
       <c r="G52" s="3">
-        <v>10300</v>
+        <v>10200</v>
       </c>
       <c r="H52" s="3">
-        <v>24800</v>
+        <v>10500</v>
       </c>
       <c r="I52" s="3">
-        <v>29300</v>
+        <v>5800</v>
       </c>
       <c r="J52" s="3">
-        <v>6100</v>
+        <v>5900</v>
       </c>
       <c r="K52" s="3">
         <v>40600</v>
@@ -2707,19 +2707,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>6100</v>
+        <v>11000</v>
       </c>
       <c r="E58" s="3">
-        <v>4700</v>
+        <v>9000</v>
       </c>
       <c r="F58" s="3">
-        <v>2400</v>
+        <v>6400</v>
       </c>
       <c r="G58" s="3">
-        <v>8500</v>
+        <v>13100</v>
       </c>
       <c r="H58" s="3">
-        <v>8300</v>
+        <v>12400</v>
       </c>
       <c r="I58" s="3">
         <v>3900</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>674800</v>
+        <v>477500</v>
       </c>
       <c r="E59" s="3">
-        <v>598300</v>
+        <v>402500</v>
       </c>
       <c r="F59" s="3">
-        <v>585200</v>
+        <v>399100</v>
       </c>
       <c r="G59" s="3">
-        <v>405200</v>
+        <v>283400</v>
       </c>
       <c r="H59" s="3">
-        <v>153900</v>
+        <v>100700</v>
       </c>
       <c r="I59" s="3">
-        <v>81600</v>
+        <v>32500</v>
       </c>
       <c r="J59" s="3">
-        <v>83100</v>
+        <v>55700</v>
       </c>
       <c r="K59" s="3">
         <v>66200</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>2383400</v>
+        <v>2424500</v>
       </c>
       <c r="E61" s="3">
-        <v>2385300</v>
+        <v>2423400</v>
       </c>
       <c r="F61" s="3">
-        <v>2385700</v>
+        <v>2429400</v>
       </c>
       <c r="G61" s="3">
-        <v>1107300</v>
+        <v>1124500</v>
       </c>
       <c r="H61" s="3">
-        <v>838700</v>
+        <v>861100</v>
       </c>
       <c r="I61" s="3">
         <v>278600</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>134900</v>
+        <v>80600</v>
       </c>
       <c r="E62" s="3">
-        <v>165100</v>
+        <v>82300</v>
       </c>
       <c r="F62" s="3">
-        <v>201900</v>
+        <v>78700</v>
       </c>
       <c r="G62" s="3">
-        <v>100100</v>
+        <v>24400</v>
       </c>
       <c r="H62" s="3">
-        <v>108500</v>
+        <v>21600</v>
       </c>
       <c r="I62" s="3">
-        <v>110300</v>
+        <v>79900</v>
       </c>
       <c r="J62" s="3">
-        <v>102100</v>
+        <v>78300</v>
       </c>
       <c r="K62" s="3">
         <v>147100</v>
@@ -3649,7 +3649,7 @@
         <v>77500</v>
       </c>
       <c r="J81" s="3">
-        <v>81700</v>
+        <v>81800</v>
       </c>
       <c r="K81" s="3">
         <v>-29900</v>
@@ -3695,25 +3695,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>91300</v>
+        <v>17300</v>
       </c>
       <c r="E83" s="3">
-        <v>96700</v>
+        <v>18100</v>
       </c>
       <c r="F83" s="3">
-        <v>74300</v>
+        <v>15900</v>
       </c>
       <c r="G83" s="3">
-        <v>58200</v>
+        <v>20400</v>
       </c>
       <c r="H83" s="3">
-        <v>48000</v>
+        <v>19700</v>
       </c>
       <c r="I83" s="3">
-        <v>26700</v>
+        <v>12900</v>
       </c>
       <c r="J83" s="3">
-        <v>27200</v>
+        <v>15600</v>
       </c>
       <c r="K83" s="3">
         <v>22500</v>
@@ -4032,10 +4032,10 @@
         <v>-12900</v>
       </c>
       <c r="E91" s="3">
-        <v>-16700</v>
+        <v>-10200</v>
       </c>
       <c r="F91" s="3">
-        <v>-13200</v>
+        <v>-11200</v>
       </c>
       <c r="G91" s="3">
         <v>-2300</v>

--- a/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
   <si>
     <t>ETSY</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2808300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2748400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2566100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2329100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1725600</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>818400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>603700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>441200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>365000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>273500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>195600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>125000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>74600</v>
       </c>
-      <c r="P8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>774600</v>
+      </c>
+      <c r="E9" s="3">
         <v>823000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>744600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>654500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>464700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>271000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>190800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>150200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>123300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>97000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>73600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>47800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>24500</v>
       </c>
-      <c r="P9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2033800</v>
+      </c>
+      <c r="E10" s="3">
         <v>1925400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1821500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1674600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1260900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>547300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>412900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>291000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>241600</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>176500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>122000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>77200</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>50100</v>
       </c>
-      <c r="P10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -875,53 +887,57 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>443100</v>
+      </c>
+      <c r="E12" s="3">
         <v>455800</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>412400</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>271500</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>180100</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>121900</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>97200</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>71400</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>55100</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>42700</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>36600</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>27500</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>18700</v>
       </c>
-      <c r="P12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,36 +980,39 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>98500</v>
+      <c r="D14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="E14" s="3">
-        <v>1047900</v>
+        <v>97300</v>
       </c>
       <c r="F14" s="3">
+        <v>1045000</v>
+      </c>
+      <c r="G14" s="3">
         <v>36700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>18700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>3900</v>
       </c>
-      <c r="I14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="J14" s="3">
+      <c r="J14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="K14" s="3">
         <v>17100</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="L14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1009,36 +1028,39 @@
       <c r="P14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>57400</v>
+      </c>
+      <c r="E15" s="3">
         <v>57000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>59400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>44300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>35600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>29300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>17200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>19000</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1054,9 +1076,12 @@
       <c r="P15" s="3">
         <v>0</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3">
+        <v>0</v>
+      </c>
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2372700</v>
+        <v>2428100</v>
       </c>
       <c r="E17" s="3">
-        <v>2176800</v>
+        <v>2373900</v>
       </c>
       <c r="F17" s="3">
+        <v>2179600</v>
+      </c>
+      <c r="G17" s="3">
         <v>1826700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1299800</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>725700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>528900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>412300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>347400</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>275400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>201800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>124300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>76000</v>
       </c>
-      <c r="P17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>375700</v>
+        <v>380200</v>
       </c>
       <c r="E18" s="3">
-        <v>389300</v>
+        <v>374500</v>
       </c>
       <c r="F18" s="3">
+        <v>386500</v>
+      </c>
+      <c r="G18" s="3">
         <v>502400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>425800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>92700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>74800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>29000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>17600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-1900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-6300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>700</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>-1400</v>
       </c>
-      <c r="P18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-13400</v>
+      </c>
+      <c r="E20" s="3">
         <v>6300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-13700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>6500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-29100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-13200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-24600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-3400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>426400</v>
+        <v>451000</v>
       </c>
       <c r="E21" s="3">
-        <v>448500</v>
+        <v>425200</v>
       </c>
       <c r="F21" s="3">
+        <v>445700</v>
+      </c>
+      <c r="G21" s="3">
         <v>560400</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>454900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>125000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>85500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>77100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-7900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>7600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>12700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5900</v>
       </c>
-      <c r="P21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E22" s="3">
         <v>14000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>9900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>42000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>24300</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>7200</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>300</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>500</v>
       </c>
-      <c r="P22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>410800</v>
+      </c>
+      <c r="E23" s="3">
         <v>292800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-662000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>471700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>365700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>80600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>55100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-2900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-28000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-2500</v>
       </c>
-      <c r="P23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>107500</v>
+      </c>
+      <c r="E24" s="3">
         <v>-14700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>32300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-21900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>16500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-15200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-22400</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-49500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26100</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-100</v>
       </c>
-      <c r="P24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E26" s="3">
         <v>307600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-694300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>493500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>349200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>95900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>77500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>81800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-29900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-54100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-15200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-2400</v>
       </c>
-      <c r="P26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E27" s="3">
         <v>307600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-694300</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>493500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>349300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>95900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>77500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>81700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-29900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-54100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-15200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-2600</v>
       </c>
-      <c r="P27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,9 +1641,12 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1611,8 +1671,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>3</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>3</v>
@@ -1629,9 +1689,12 @@
       <c r="P29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>13400</v>
+      </c>
+      <c r="E32" s="3">
         <v>-6300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>13700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-6500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>29100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>13200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>24600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>3400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E33" s="3">
         <v>307600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-694300</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>493500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>349200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>95900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>77500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>81800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-29900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-54100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-15200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-2600</v>
       </c>
-      <c r="P33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E35" s="3">
         <v>307600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-694300</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>493500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>349200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>95900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>77500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>81800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-29900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-54100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-15200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-2600</v>
       </c>
-      <c r="P35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,143 +2073,153 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>811200</v>
+      </c>
+      <c r="E41" s="3">
         <v>914300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>921300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>780200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>1244100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>443300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>367000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>315400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>181600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>271200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>69700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>36800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>34900</v>
       </c>
-      <c r="P41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>228300</v>
+      </c>
+      <c r="E42" s="3">
         <v>236100</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>250400</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>204400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>425100</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>374000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>257300</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>25100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>100500</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>21600</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>19200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>18100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>20800</v>
       </c>
-      <c r="P42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>8700</v>
+      </c>
+      <c r="E43" s="3">
         <v>24700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>27900</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>22600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>15400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>12200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>33700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>56200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>39500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>26000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>16400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9500</v>
       </c>
-      <c r="P43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2149,8 +2244,8 @@
       <c r="J44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="L44" s="3">
         <v>0</v>
@@ -2167,120 +2262,129 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>189600</v>
+      </c>
+      <c r="E45" s="3">
         <v>265400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>234000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>220200</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>146800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>49800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>21100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>44700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>32700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>26700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>15200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3500</v>
       </c>
-      <c r="P45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1327700</v>
+      </c>
+      <c r="E46" s="3">
         <v>1570400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1513700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1341500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1894800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>921000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>680300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>439300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>371000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>359100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>127100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>76800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>68800</v>
       </c>
-      <c r="P46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>111700</v>
+      </c>
+      <c r="E47" s="3">
         <v>86700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>29100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>85000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>39100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>89300</v>
       </c>
-      <c r="I47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="J47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2296,105 +2400,114 @@
       <c r="N47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3">
+        <v>0</v>
+      </c>
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>278900</v>
+      </c>
+      <c r="E48" s="3">
         <v>291900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>288500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>321000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>132100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>66800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>89400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>99300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>126400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>105000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>151100</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>23100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18200</v>
       </c>
-      <c r="P48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>551000</v>
+      </c>
+      <c r="E49" s="3">
         <v>595500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>673100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1978200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>328300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>440400</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>102900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>61000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>43200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>30600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>41700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>5800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5300</v>
       </c>
-      <c r="P49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E52" s="3">
         <v>3000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>8900</v>
-      </c>
-      <c r="F52" s="3">
-        <v>10200</v>
       </c>
       <c r="G52" s="3">
         <v>10200</v>
       </c>
       <c r="H52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I52" s="3">
         <v>10500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5900</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>40600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>58400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7400</v>
-      </c>
-      <c r="N52" s="3">
-        <v>400</v>
       </c>
       <c r="O52" s="3">
         <v>400</v>
       </c>
-      <c r="P52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P52" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2417800</v>
+      </c>
+      <c r="E54" s="3">
         <v>2685400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2635000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3831800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>2404500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>1542400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>901900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>605600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>581200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>553100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>246200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>106200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>92600</v>
       </c>
-      <c r="P54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E57" s="3">
         <v>29900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>28800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>40900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>26300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>13600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>11000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>14400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>8200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>5300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>3500</v>
       </c>
-      <c r="P57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>11300</v>
+      </c>
+      <c r="E58" s="3">
         <v>11000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>9000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>13100</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>3900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>6800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1300</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>477500</v>
+        <v>403500</v>
       </c>
       <c r="E59" s="3">
+        <v>453200</v>
+      </c>
+      <c r="F59" s="3">
         <v>402500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>399100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>283400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>100700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>32500</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>55700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>66200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>60100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>31500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>13100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>6200</v>
       </c>
-      <c r="P59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>665100</v>
+      </c>
+      <c r="E60" s="3">
         <v>710800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>631800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>615600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>454700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>188500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>112100</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>102500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>84000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>80100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>41500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>19200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10900</v>
       </c>
-      <c r="P60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2422900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2424500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2423400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2429400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1124500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>861100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>278600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>4100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>3100</v>
       </c>
-      <c r="N61" s="3">
-        <v>0</v>
-      </c>
       <c r="O61" s="3">
+        <v>0</v>
+      </c>
+      <c r="P61" s="3">
         <v>800</v>
       </c>
-      <c r="P61" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3">
+        <v>0</v>
+      </c>
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>80700</v>
+      </c>
+      <c r="E62" s="3">
         <v>80600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>82300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>78700</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>21600</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>79900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>78300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>147100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>134900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>54300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>2700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1000</v>
       </c>
-      <c r="P62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3176600</v>
+      </c>
+      <c r="E66" s="3">
         <v>3229100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3182200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3203200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>1662100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1135700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>501000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>208700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>236400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>222600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>98900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>21900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>12700</v>
       </c>
-      <c r="P66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,9 +3378,12 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3248,7 +3415,7 @@
         <v>0</v>
       </c>
       <c r="M70" s="3">
-        <v>80200</v>
+        <v>0</v>
       </c>
       <c r="N70" s="3">
         <v>80200</v>
@@ -3257,11 +3424,14 @@
         <v>80200</v>
       </c>
       <c r="P70" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+        <v>80200</v>
+      </c>
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-1784000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1357400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1048300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>71700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-146800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-227400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-153400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-96300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-116300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-86400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-32400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-17100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-16000</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-758900</v>
+      </c>
+      <c r="E76" s="3">
         <v>-543700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-547300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>628600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>742400</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>406600</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>400900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>396900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>344800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>330500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>67100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>4000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-300</v>
       </c>
-      <c r="P76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>303300</v>
+      </c>
+      <c r="E81" s="3">
         <v>307600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-694300</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>493500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>349200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>95900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>77500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>81800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-29900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-54100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-15200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-2600</v>
       </c>
-      <c r="P81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E83" s="3">
         <v>17300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>18100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>15900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>20400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>19700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>12900</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>15600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>22500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>18600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>17200</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>12400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7900</v>
       </c>
-      <c r="P83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>752500</v>
+      </c>
+      <c r="E89" s="3">
         <v>705500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>683600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>651600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>679000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>206900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>198900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>69100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>48000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>33200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>12100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>16500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>9700</v>
       </c>
-      <c r="P89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-36500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-3900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-36000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-6500</v>
       </c>
-      <c r="P91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-53100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-73300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-30000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-1558000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-488400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-285400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>61800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-135400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-23300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-20700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-15000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-28900</v>
       </c>
-      <c r="P94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,8 +4454,9 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4266,9 +4499,12 @@
       <c r="P96" s="3">
         <v>0</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3">
+        <v>0</v>
+      </c>
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,142 +4643,154 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-787200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-656500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-506500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>452700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>119300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>359600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>144000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>6600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>195700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>45200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>43000</v>
       </c>
-      <c r="P100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15300</v>
+      </c>
+      <c r="E101" s="3">
         <v>12000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-10200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>13900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1800</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-1700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-4000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>400</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-103100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-12300</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>141100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-463900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>800800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>76300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>51500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>133900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-89700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>201600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>32900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>23800</v>
       </c>
-      <c r="P102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q102" s="3"/>
+      <c r="Q102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/ETSY_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="92">
   <si>
     <t>ETSY</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="4.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R7" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D8" s="3">
+        <v>2883500</v>
+      </c>
+      <c r="E8" s="3">
         <v>2808300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2748400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2566100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2329100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>1725600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>818400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>603700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>441200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>365000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>273500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>195600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>125000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>74600</v>
       </c>
-      <c r="Q8" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R8" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D9" s="3">
+        <v>817800</v>
+      </c>
+      <c r="E9" s="3">
         <v>774600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>823000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>744600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>654500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>464700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>271000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>190800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>150200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>123300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>97000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>73600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>47800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>24500</v>
       </c>
-      <c r="Q9" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
       <c r="D10" s="3">
+        <v>2065700</v>
+      </c>
+      <c r="E10" s="3">
         <v>2033800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>1925400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1821500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1674600</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>1260900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>547300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>412900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>291000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>241600</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>176500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>122000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>77200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>50100</v>
       </c>
-      <c r="Q10" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R10" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -888,56 +900,60 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
       <c r="D12" s="3">
+        <v>450200</v>
+      </c>
+      <c r="E12" s="3">
         <v>443100</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>455800</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>412400</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>271500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>180100</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>121900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>97200</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>71400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>55100</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>42700</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>36600</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>27500</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>18700</v>
       </c>
-      <c r="Q12" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,39 +999,42 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D14" s="3">
+        <v>106800</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3">
         <v>97300</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1045000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>36700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>18700</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>3900</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="3">
         <v>17100</v>
       </c>
-      <c r="L14" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="M14" s="3" t="s">
         <v>3</v>
       </c>
@@ -1031,39 +1050,42 @@
       <c r="Q14" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>50900</v>
+      </c>
+      <c r="E15" s="3">
         <v>57400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>57000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>59400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>44300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>35600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>29300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>17200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>19000</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1079,9 +1101,12 @@
       <c r="Q15" s="3">
         <v>0</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R15" s="3">
+        <v>0</v>
+      </c>
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2515600</v>
+      </c>
+      <c r="E17" s="3">
         <v>2428100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2373900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2179600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>1826700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>1299800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>725700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>528900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>412300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>347400</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>275400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>201800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>124300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>76000</v>
       </c>
-      <c r="Q17" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R17" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>367900</v>
+      </c>
+      <c r="E18" s="3">
         <v>380200</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>374500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>386500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>502400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>425800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>92700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>74800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>29000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>17600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-1900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-6300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>700</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q18" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R18" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>40400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-13400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>6300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-13700</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>6500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>6500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-13200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-24600</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-3400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-700</v>
       </c>
-      <c r="Q20" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R20" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>378400</v>
+      </c>
+      <c r="E21" s="3">
         <v>451000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>425200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>445700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>560400</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>454900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>125000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>85500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>77100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-7900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>7600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>12700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5900</v>
       </c>
-      <c r="Q21" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R21" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E22" s="3">
         <v>13800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>42000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>24300</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>7200</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>600</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>300</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>500</v>
       </c>
-      <c r="Q22" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>246700</v>
+      </c>
+      <c r="E23" s="3">
         <v>410800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>292800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-662000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>471700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>365700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>80600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>55100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>32300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-2900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-28000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10300</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q23" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R23" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>83700</v>
+      </c>
+      <c r="E24" s="3">
         <v>107500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-14700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>32300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-21900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>16500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-15200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-22400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-49500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>27000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26100</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-100</v>
       </c>
-      <c r="Q24" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E26" s="3">
         <v>303300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>307600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-694300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>493500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>349200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>95900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>77500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>81800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-29900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-54100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-15200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-2400</v>
       </c>
-      <c r="Q26" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R26" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E27" s="3">
         <v>303300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>307600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-694300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>493500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>349300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>95900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>77500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>81700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-29900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-54100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-15200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q27" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R27" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,9 +1701,12 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1674,8 +1734,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>3</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>3</v>
@@ -1692,9 +1752,12 @@
       <c r="Q29" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R29" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-40400</v>
+      </c>
+      <c r="E32" s="3">
         <v>13400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-6300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>13700</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-6500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-6500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>13200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>24600</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>3400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>700</v>
       </c>
-      <c r="Q32" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R32" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E33" s="3">
         <v>303300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>307600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-694300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>493500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>349200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>95900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>77500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>81800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-29900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-54100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-15200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q33" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R33" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E35" s="3">
         <v>303300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>307600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-694300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>493500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>349200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>95900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>77500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>81800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-29900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-54100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-15200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q35" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R35" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R38" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,104 +2159,111 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>1395800</v>
+      </c>
+      <c r="E41" s="3">
         <v>811200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>914300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>921300</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>780200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>1244100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>443300</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>367000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>315400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>181600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>271200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>69700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>36800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>34900</v>
       </c>
-      <c r="Q41" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R41" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>224100</v>
+      </c>
+      <c r="E42" s="3">
         <v>228300</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>236100</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>250400</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>204400</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>425100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>374000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>257300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>25100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>100500</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>21600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>19200</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>18100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>20800</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R42" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -2179,47 +2271,50 @@
         <v>8700</v>
       </c>
       <c r="E43" s="3">
+        <v>8700</v>
+      </c>
+      <c r="F43" s="3">
         <v>24700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>27900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>27300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>22600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>15400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>12200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>33700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>56200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>39500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>26000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>16400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>9500</v>
       </c>
-      <c r="Q43" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R43" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2247,8 +2342,8 @@
       <c r="K44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="L44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2265,129 +2360,138 @@
       <c r="Q44" s="3">
         <v>0</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>205000</v>
+      </c>
+      <c r="E45" s="3">
         <v>189600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>265400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>234000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>220200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>146800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>49800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21100</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>44700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>32700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>26700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>15200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3500</v>
       </c>
-      <c r="Q45" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R45" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>1961000</v>
+      </c>
+      <c r="E46" s="3">
         <v>1327700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>1570400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>1513700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>1341500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1894800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>921000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>680300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>439300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>371000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>359100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>127100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>76800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>68800</v>
       </c>
-      <c r="Q46" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R46" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>134400</v>
+      </c>
+      <c r="E47" s="3">
         <v>111700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>86700</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>29100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>85000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>39100</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>89300</v>
       </c>
-      <c r="J47" s="3" t="s">
-        <v>3</v>
-      </c>
       <c r="K47" s="3" t="s">
         <v>3</v>
       </c>
@@ -2403,111 +2507,120 @@
       <c r="O47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R47" s="3">
+        <v>0</v>
+      </c>
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>265300</v>
+      </c>
+      <c r="E48" s="3">
         <v>278900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>291900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>288500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>321000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>132100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>66800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>89400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>99300</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>126400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>105000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>151100</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>23100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>18200</v>
       </c>
-      <c r="Q48" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R48" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>335400</v>
+      </c>
+      <c r="E49" s="3">
         <v>551000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>595500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>673100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1978200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>328300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>440400</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>102900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>61000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>43200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>30600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>41700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>5800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5300</v>
       </c>
-      <c r="Q49" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R49" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>11900</v>
+      </c>
+      <c r="E52" s="3">
         <v>2900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>3000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>8900</v>
-      </c>
-      <c r="G52" s="3">
-        <v>10200</v>
       </c>
       <c r="H52" s="3">
         <v>10200</v>
       </c>
       <c r="I52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J52" s="3">
         <v>10500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>5900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>40600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7400</v>
-      </c>
-      <c r="O52" s="3">
-        <v>400</v>
       </c>
       <c r="P52" s="3">
         <v>400</v>
       </c>
-      <c r="Q52" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3">
+        <v>400</v>
+      </c>
+      <c r="R52" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>2827300</v>
+      </c>
+      <c r="E54" s="3">
         <v>2417800</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>2685400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>2635000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3831800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>2404500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>1542400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>901900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>605600</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>581200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>553100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>246200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>106200</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>92600</v>
       </c>
-      <c r="Q54" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R54" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>28800</v>
+      </c>
+      <c r="E57" s="3">
         <v>26000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>29900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>28800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>28000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>40900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>26300</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>26500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>13600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>11000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>14400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>8200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>5300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>3500</v>
       </c>
-      <c r="Q57" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R57" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>650700</v>
+      </c>
+      <c r="E58" s="3">
         <v>11300</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>11000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>9000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>13100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>3900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6800</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1300</v>
       </c>
-      <c r="Q58" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R58" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>445500</v>
+      </c>
+      <c r="E59" s="3">
         <v>403500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>453200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>402500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>399100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>283400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>100700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>32500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>55700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>66200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>60100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>31500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>13100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>6200</v>
       </c>
-      <c r="Q59" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R59" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1363600</v>
+      </c>
+      <c r="E60" s="3">
         <v>665100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>710800</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>631800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>615600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>454700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>188500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>112100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>102500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>80100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>19200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10900</v>
       </c>
-      <c r="Q60" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R60" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2464500</v>
+      </c>
+      <c r="E61" s="3">
         <v>2422900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2424500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2423400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2429400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1124500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>861100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>278600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>4100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>7600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3100</v>
       </c>
-      <c r="O61" s="3">
-        <v>0</v>
-      </c>
       <c r="P61" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="3">
         <v>800</v>
       </c>
-      <c r="Q61" s="3">
-        <v>0</v>
-      </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R61" s="3">
+        <v>0</v>
+      </c>
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>88500</v>
+      </c>
+      <c r="E62" s="3">
         <v>80700</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>80600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>82300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>78700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>21600</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>79900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>78300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>147100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>134900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>54300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>2700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1000</v>
       </c>
-      <c r="Q62" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R62" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>3925300</v>
+      </c>
+      <c r="E66" s="3">
         <v>3176600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>3229100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>3182200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>3203200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>1662100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>1135700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>501000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>208700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>236400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>222600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>98900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>21900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>12700</v>
       </c>
-      <c r="Q66" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R66" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3418,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="N70" s="3">
-        <v>80200</v>
+        <v>0</v>
       </c>
       <c r="O70" s="3">
         <v>80200</v>
@@ -3427,11 +3594,14 @@
         <v>80200</v>
       </c>
       <c r="Q70" s="3">
-        <v>0</v>
-      </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+        <v>80200</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-2404000</v>
+      </c>
+      <c r="E72" s="3">
         <v>-1784000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-1357400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-1048300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>71700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-146800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-227400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-153400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-96300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-116300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-86400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-32400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-17100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-16000</v>
       </c>
-      <c r="Q72" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R72" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1098100</v>
+      </c>
+      <c r="E76" s="3">
         <v>-758900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-543700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-547300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>628600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>742400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>406600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>400900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>396900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>344800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>330500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>67100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>4000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-300</v>
       </c>
-      <c r="Q76" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R76" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R80" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>163000</v>
+      </c>
+      <c r="E81" s="3">
         <v>303300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>307600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-694300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>493500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>349200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>95900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>77500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>81800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-29900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-54100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-15200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-2600</v>
       </c>
-      <c r="Q81" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R81" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E83" s="3">
         <v>19300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>17300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>18100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>15900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>20400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>12900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>15600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>22500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>18600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>17200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>12400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7900</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R83" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>693400</v>
+      </c>
+      <c r="E89" s="3">
         <v>752500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>705500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>683600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>651600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>679000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>206900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>198900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>69100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>48000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>33200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>12100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>16500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>9700</v>
       </c>
-      <c r="Q89" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R89" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-15400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14200</v>
       </c>
-      <c r="E91" s="3">
-        <v>-12900</v>
-      </c>
       <c r="F91" s="3">
+        <v>-13000</v>
+      </c>
+      <c r="G91" s="3">
         <v>-10200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11200</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-2300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-36500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-3900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-36000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11100</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-6500</v>
       </c>
-      <c r="Q91" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R91" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>32100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-53100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-73300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-1558000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-488400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-285400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>61800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-135400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-23300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-20700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28900</v>
       </c>
-      <c r="Q94" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R94" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4502,9 +4735,12 @@
       <c r="Q96" s="3">
         <v>0</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R96" s="3">
+        <v>0</v>
+      </c>
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,151 +4888,163 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-169900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-787200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-656500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-506500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>452700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>119300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>359600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>144000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>6600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>195700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>45200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>43000</v>
       </c>
-      <c r="Q100" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R100" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15300</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>12000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-10200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>13900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-1800</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-6000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-1700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-4000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>400</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q101" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>593200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-103100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-12300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>141100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-463900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>76300</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>51500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>133900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-89700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>201600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>32900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>23800</v>
       </c>
-      <c r="Q102" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="R102" s="3"/>
+      <c r="R102" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
